--- a/data/trans_camb/P38C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Habitat-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,84</t>
+          <t>-2,2; 7,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,5</t>
+          <t>1,8; 7,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,8</t>
+          <t>1,15; 6,76</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 9,63</t>
+          <t>-2,51; 9,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,72</t>
+          <t>2,02; 9,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,16</t>
+          <t>1,32; 8,06</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-47,89; -3,29</t>
+          <t>-50,94; -3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -2,97</t>
+          <t>-8,41; -2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,18; -4,26</t>
+          <t>-38,18; -4,03</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,8; -3,96</t>
+          <t>-62,17; -3,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -3,3</t>
+          <t>-9,12; -2,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,86; -4,96</t>
+          <t>-43,72; -4,78</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 3,98</t>
+          <t>-6,75; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,59</t>
+          <t>-2,38; 8,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,8</t>
+          <t>-2,44; 7,43</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 5,11</t>
+          <t>-8,27; 4,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 9,96</t>
+          <t>-2,73; 9,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 8,24</t>
+          <t>-2,92; 8,96</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 3,48</t>
+          <t>-4,66; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 3,25</t>
+          <t>-18,73; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 1,92</t>
+          <t>-11,16; 1,62</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,41</t>
+          <t>-5,67; 4,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 3,79</t>
+          <t>-21,88; 3,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 2,33</t>
+          <t>-13,4; 1,96</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -0,38</t>
+          <t>-22,03; -0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,64</t>
+          <t>-6,64; 1,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 0,07</t>
+          <t>-11,95; 0,01</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -0,46</t>
+          <t>-27,36; -0,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,88</t>
+          <t>-7,62; 1,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 0,09</t>
+          <t>-14,14; -0,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,35</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,64</t>
+          <t>-1,81; 7,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,91</t>
+          <t>0,56; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,76</t>
+          <t>0,35; 6,1</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 9,43</t>
+          <t>-2,12; 9,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,25</t>
+          <t>0,66; 8,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,06</t>
+          <t>0,4; 7,29</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-20,5</t>
+          <t>-5,39</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-5,46</t>
+          <t>-5,9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,31</t>
+          <t>-5,67</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-50,94; -3,24</t>
+          <t>-9,43; -1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -2,65</t>
+          <t>-8,82; -2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,18; -4,03</t>
+          <t>-8,15; -3,12</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-24,88%</t>
+          <t>-6,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-6,03%</t>
+          <t>-6,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-16,55%</t>
+          <t>-6,56%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,17; -3,94</t>
+          <t>-11,26; -1,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -2,94</t>
+          <t>-9,72; -3,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,72; -4,78</t>
+          <t>-9,31; -3,64</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>-1,85</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,58</t>
+          <t>-6,98; 2,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,45</t>
+          <t>-5,02; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,43</t>
+          <t>-5,32; 0,72</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-1,38%</t>
+          <t>-2,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>-1,65%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>-2,21%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 4,44</t>
+          <t>-8,56; 3,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 9,94</t>
+          <t>-5,64; 3,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,96</t>
+          <t>-6,17; 0,89</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,74</t>
+          <t>-6,26; 2,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,25</t>
+          <t>-1,87; 4,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 1,62</t>
+          <t>-2,95; 2,52</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0,68%</t>
+          <t>-2,42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-3,97%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>-0,23%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,79</t>
+          <t>-7,59; 2,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 3,85</t>
+          <t>-2,18; 5,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 1,96</t>
+          <t>-3,52; 3,1</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-6,81</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -0,25</t>
+          <t>-4,14; 0,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,35</t>
+          <t>-2,47; 0,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,01</t>
+          <t>-2,84; -0,13</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-8,35%</t>
+          <t>-2,6%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,03%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,6%</t>
+          <t>-1,76%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,36; -0,3</t>
+          <t>-5,01; 0,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,54</t>
+          <t>-2,79; 0,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -0,03</t>
+          <t>-3,35; -0,16</t>
         </is>
       </c>
     </row>
